--- a/data/trans_bre/IP07_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP07_R-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-1,05</t>
+          <t>-0,79</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-1,27%</t>
+          <t>-0,97%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 14,44</t>
+          <t>-1,47; 14,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 11,53</t>
+          <t>-5,84; 11,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,04; 6,76</t>
+          <t>-6,77; 7,14</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,44; 10,79</t>
+          <t>-11,67; 10,39</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 19,95</t>
+          <t>-1,82; 20,29</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,71; 16,9</t>
+          <t>-7,36; 16,48</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-6,68; 8,07</t>
+          <t>-7,31; 8,61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-13,28; 13,78</t>
+          <t>-13,31; 13,51</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0,33</t>
+          <t>-1,64</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-0,42%</t>
+          <t>-2,11%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,13; 6,13</t>
+          <t>-5,95; 5,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 8,17</t>
+          <t>-3,5; 7,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 4,73</t>
+          <t>-5,69; 4,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-7,89; 6,74</t>
+          <t>-9,19; 5,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-7,78; 8,31</t>
+          <t>-7,62; 7,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 11,22</t>
+          <t>-4,53; 10,61</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-5,97; 5,49</t>
+          <t>-6,27; 4,98</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-9,63; 9,16</t>
+          <t>-11,47; 7,98</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,19</t>
+          <t>-0,8</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-0,26%</t>
+          <t>-1,07%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 11,47</t>
+          <t>-6,64; 10,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,81; 6,69</t>
+          <t>-10,4; 6,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,8; 12,78</t>
+          <t>1,29; 12,49</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,11; 7,98</t>
+          <t>-8,35; 7,19</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,87; 16,92</t>
+          <t>-8,52; 14,87</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-12,86; 9,51</t>
+          <t>-13,5; 9,46</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,94; 16,11</t>
+          <t>1,5; 15,94</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-10,69; 11,27</t>
+          <t>-10,76; 10,18</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3,31</t>
+          <t>3,11</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,17%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-9,1; 4,06</t>
+          <t>-9,2; 4,37</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-9,55; 5,63</t>
+          <t>-8,97; 6,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,8; 5,38</t>
+          <t>-7,87; 4,53</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,8; 13,64</t>
+          <t>-4,51; 11,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-11,21; 5,3</t>
+          <t>-11,31; 5,84</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-12,25; 7,96</t>
+          <t>-11,28; 8,77</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-8,87; 6,43</t>
+          <t>-8,77; 5,47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-6,13; 19,96</t>
+          <t>-5,7; 16,7</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,21</t>
+          <t>0,7</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 4,74</t>
+          <t>-2,71; 4,39</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 4,26</t>
+          <t>-3,11; 4,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 3,89</t>
+          <t>-1,7; 4,19</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 6,54</t>
+          <t>-3,72; 5,41</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 6,4</t>
+          <t>-3,43; 5,86</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 5,83</t>
+          <t>-4,09; 6,2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 4,62</t>
+          <t>-1,92; 4,96</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 8,92</t>
+          <t>-4,79; 7,4</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP07_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP07_R-Edad-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>6,49</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>3,24</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,15</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-0,79</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>8,34%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>4,43%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-0,97%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>6.490603839123732</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>3.240324557732566</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.1461052479335478</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-0.7907892872734745</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.08343185357961409</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.04433420374526374</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0.001663583557522443</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-0.009676591729012423</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-1,47; 14,69</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-5,84; 11,48</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-6,77; 7,14</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-11,67; 10,39</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-1,82; 20,29</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-7,36; 16,48</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-7,31; 8,61</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-13,31; 13,51</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-1.470262624577666</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-5.841976436955096</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-6.771348945616188</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-11.66979408016582</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.01821962444259218</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.07357733336611195</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.07307496200651477</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.1330884088740907</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>14.6925642913091</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>11.47934535456933</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>7.142858819971732</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>10.39422952674654</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.202891916032123</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.1648019066667613</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.08612938800681917</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0.1351321333637941</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0,02</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>2,23</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-0,33</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-1,64</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,03%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2,93%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-0,37%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-2,11%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-5,95; 5,91</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-3,5; 7,86</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-5,69; 4,25</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-9,19; 5,88</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-7,62; 7,97</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-4,53; 10,61</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-6,27; 4,98</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-11,47; 7,98</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>0.01972183954745965</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>2.22881086250899</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-0.3261693677259814</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-1.638035328031362</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.0002577570267946579</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.02925225140853924</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.003725647489331264</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.02109601889260388</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>2,55</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-2,16</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>6,95</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,8</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>3,45%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-2,92%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>8,47%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-1,07%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-5.950404626194905</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-3.504297620650682</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-5.687953761656487</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-9.19137748719068</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.07622159193798467</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.04527483358607844</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.06274877373596194</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.1147448378730539</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-6,64; 10,34</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-10,4; 6,42</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>1,29; 12,49</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-8,35; 7,19</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-8,52; 14,87</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-13,5; 9,46</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>1,5; 15,94</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-10,76; 10,18</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>5.908250711582967</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>7.859290319542099</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>4.250819703278634</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>5.882668291133597</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.07968683915041451</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.1060639639249754</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.04982779828620629</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.07975345201322818</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +819,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-2,06</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-1,42</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-1,71</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3,11</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-2,64%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-1,9%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-1,98%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>4,17%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>2.548110422919903</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-2.156897523735535</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>6.947079395006083</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-0.7958535473558404</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.03450232637171097</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.02919833937504986</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.08470957693907667</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.01071648527339811</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-9,2; 4,37</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-8,97; 6,24</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-7,87; 4,53</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-4,51; 11,3</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-11,31; 5,84</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-11,28; 8,77</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-8,77; 5,47</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-5,7; 16,7</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-6.636665047699523</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-10.4011272838638</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>1.288861200692359</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-8.345167161398891</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.08516436343710164</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.1350474745751759</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>0.01501941793673255</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.1076219748377568</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>10.34153986169003</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>6.420947306505082</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>12.49364458270252</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>7.191264314753311</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.1486767577226614</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.09459427399402888</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.1594208016879218</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.1018358634043001</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-2.062244575318806</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-1.419754113761351</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-1.709556355153119</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>3.114275736472871</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.02637674625537188</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.01902505533509556</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.01980071139795694</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>0.0417129363466486</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-9.202879610080346</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-8.968890595929556</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-7.866932448002709</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-4.509769710145907</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.1131473270228883</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.1127949919960719</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.08768534263862042</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.0570023686940894</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>4.369950631134762</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>6.241960345274495</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>4.528887810592376</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>11.30242038047814</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.05842543695443891</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.08771457464578543</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.05473208388051157</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.166987746147815</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>0,92</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0,52</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1,28</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,7</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1,2%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>1,49%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-2,71; 4,39</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-3,11; 4,57</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-1,7; 4,19</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-3,72; 5,41</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-3,43; 5,86</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-4,09; 6,2</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-1,92; 4,96</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-4,79; 7,4</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>0.918125810755166</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.5241637162469059</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>1.284255026577197</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0.6996279087426616</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.01197319774357711</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.007014647894300203</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.01494969563068265</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>0.00923876211332811</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-2.709859292246793</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-3.112594480507652</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-1.702993962960095</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-3.724240720672744</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.034295424197844</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.04088113669299741</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.0191666009111353</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.04791329072694978</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>4.393430354182155</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>4.567908436957992</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>4.193498727192062</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>5.407113254850348</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.05863033773966098</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.06204167827054349</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.04959591304471775</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.07402314849504189</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1117,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
